--- a/LLM_Extraction_and_CrossCritique/interactive-table/results/pipeline_comparison_p1_vs_p3.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/results/pipeline_comparison_p1_vs_p3.xlsx
@@ -816,16 +816,16 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E2">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F2">
-        <v>0.7407407407407408</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -848,16 +848,16 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F3">
-        <v>0.6666666666666666</v>
+        <v>0.7407407407407408</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -886,10 +886,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.5</v>
+        <v>0.7925925925925926</v>
       </c>
       <c r="F4">
-        <v>0.5555555555555556</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -944,10 +944,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0.4000000000000001</v>
@@ -1072,16 +1072,16 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0.4333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F10">
-        <v>0.6190476190476191</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1206,10 +1206,10 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F14">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1238,10 +1238,10 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F15">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1264,16 +1264,16 @@
         <v>24</v>
       </c>
       <c r="C16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F16">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G16">
         <v>0.5</v>
@@ -1296,16 +1296,16 @@
         <v>25</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E17">
-        <v>0.4000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F17">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G17">
         <v>0.3333333333333333</v>
@@ -1334,10 +1334,10 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F18">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1360,16 +1360,16 @@
         <v>27</v>
       </c>
       <c r="C19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E19">
-        <v>0.4666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F19">
-        <v>0.5833333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1392,16 +1392,16 @@
         <v>28</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E20">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F20">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1430,10 +1430,10 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F21">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G21">
         <v>0.6666666666666666</v>
@@ -1456,16 +1456,16 @@
         <v>30</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D22">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E22">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F22">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G22">
         <v>0.6666666666666666</v>
@@ -1488,16 +1488,16 @@
         <v>31</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E23">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F23">
-        <v>0.8333333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="G23">
         <v>0.75</v>
@@ -1552,16 +1552,16 @@
         <v>33</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F25">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1590,10 +1590,10 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>0.4000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="F26">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1616,16 +1616,16 @@
         <v>35</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>0.5</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F27">
-        <v>0.625</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1686,10 +1686,10 @@
         <v>1</v>
       </c>
       <c r="E29">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F29">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1712,16 +1712,16 @@
         <v>38</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F30">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1750,10 +1750,10 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F31">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1776,7 +1776,7 @@
         <v>40</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1840,16 +1840,16 @@
         <v>42</v>
       </c>
       <c r="C34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>0.4333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F34">
-        <v>0.5416666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G34">
         <v>0.5</v>
@@ -1878,10 +1878,10 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>0.4666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F35">
-        <v>0.5833333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1904,16 +1904,16 @@
         <v>44</v>
       </c>
       <c r="C36">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D36">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E36">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F36">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G36">
         <v>0.5</v>
@@ -1942,10 +1942,10 @@
         <v>1</v>
       </c>
       <c r="E37">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F37">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -1974,10 +1974,10 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.4000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F38">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -2006,10 +2006,10 @@
         <v>1</v>
       </c>
       <c r="E39">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F39">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2064,7 +2064,7 @@
         <v>49</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2134,10 +2134,10 @@
         <v>1</v>
       </c>
       <c r="E43">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F43">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2166,10 +2166,10 @@
         <v>1</v>
       </c>
       <c r="E44">
-        <v>0.6333333333333333</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F44">
-        <v>0.7916666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2198,10 +2198,10 @@
         <v>1</v>
       </c>
       <c r="E45">
-        <v>0.4000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="F45">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2224,16 +2224,16 @@
         <v>54</v>
       </c>
       <c r="C46">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>0.5666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="F46">
-        <v>0.7083333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="G46">
         <v>0.5</v>
@@ -2256,16 +2256,16 @@
         <v>55</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E47">
-        <v>0.4000000000000001</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F47">
-        <v>0.5</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -2288,16 +2288,16 @@
         <v>56</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>0.4000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="F48">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -2320,16 +2320,16 @@
         <v>57</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F49">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -2352,16 +2352,16 @@
         <v>58</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F50">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -2390,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0.5666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="F51">
-        <v>0.7083333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2416,10 +2416,10 @@
         <v>60</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E52">
         <v>0.6</v>
@@ -2454,10 +2454,10 @@
         <v>1</v>
       </c>
       <c r="E53">
-        <v>0.4666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F53">
-        <v>0.5833333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -2483,13 +2483,13 @@
         <v>1</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E54">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F54">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E55">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F55">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -2547,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E56">
         <v>0.6</v>
@@ -2614,10 +2614,10 @@
         <v>1</v>
       </c>
       <c r="E58">
-        <v>0.6111111111111112</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F58">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2646,10 +2646,10 @@
         <v>1</v>
       </c>
       <c r="E59">
-        <v>0.5</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="F59">
-        <v>0.625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2672,10 +2672,10 @@
         <v>68</v>
       </c>
       <c r="C60">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D60">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="E60">
         <v>0.5</v>
@@ -2710,10 +2710,10 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <v>0.5</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F61">
-        <v>0.7142857142857143</v>
+        <v>0.8095238095238094</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2742,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.4000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F62">
-        <v>0.4444444444444444</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2768,16 +2768,16 @@
         <v>71</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>0.4000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="F63">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -2806,10 +2806,10 @@
         <v>1</v>
       </c>
       <c r="E64">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F64">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -2832,16 +2832,16 @@
         <v>73</v>
       </c>
       <c r="C65">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F65">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -2864,16 +2864,16 @@
         <v>74</v>
       </c>
       <c r="C66">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="D66">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="E66">
-        <v>0.5666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="F66">
-        <v>0.7083333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="G66">
         <v>0.6666666666666666</v>
@@ -2896,16 +2896,16 @@
         <v>75</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E67">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F67">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -2934,10 +2934,10 @@
         <v>0.5</v>
       </c>
       <c r="E68">
-        <v>0.4000000000000001</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F68">
-        <v>0.5714285714285714</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -2960,10 +2960,10 @@
         <v>77</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="D69">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E69">
         <v>0.5</v>
@@ -2992,10 +2992,10 @@
         <v>78</v>
       </c>
       <c r="C70">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E70">
         <v>0.5</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F71">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -3056,13 +3056,13 @@
         <v>80</v>
       </c>
       <c r="C72">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F72">
         <v>0.8333333333333334</v>
@@ -3094,10 +3094,10 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F73">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3126,10 +3126,10 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>0.5666666666666667</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F74">
-        <v>0.7083333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3158,10 +3158,10 @@
         <v>1</v>
       </c>
       <c r="E75">
-        <v>0.4000000000000001</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="F75">
-        <v>0.5714285714285714</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -3190,10 +3190,10 @@
         <v>1</v>
       </c>
       <c r="E76">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F76">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3222,10 +3222,10 @@
         <v>1</v>
       </c>
       <c r="E77">
-        <v>0.5666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="F77">
-        <v>0.7083333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -3254,10 +3254,10 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <v>0.5</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F78">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -3280,16 +3280,16 @@
         <v>87</v>
       </c>
       <c r="C79">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F79">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G79">
         <v>0.5</v>
@@ -3318,10 +3318,10 @@
         <v>1</v>
       </c>
       <c r="E80">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F80">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3350,10 +3350,10 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F81">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3376,16 +3376,16 @@
         <v>90</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E82">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F82">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>91</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3440,7 +3440,7 @@
         <v>92</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3472,16 +3472,16 @@
         <v>93</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F85">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -3504,16 +3504,16 @@
         <v>94</v>
       </c>
       <c r="C86">
-        <v>0.7777777777777777</v>
+        <v>0.5</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E86">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F86">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G86">
         <v>0.5</v>
@@ -3542,10 +3542,10 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0.5666666666666667</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F87">
-        <v>0.7083333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -3574,10 +3574,10 @@
         <v>1</v>
       </c>
       <c r="E88">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F88">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G88">
         <v>0.6666666666666666</v>
@@ -3600,16 +3600,16 @@
         <v>97</v>
       </c>
       <c r="C89">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F89">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G89">
         <v>0.5</v>
@@ -3638,10 +3638,10 @@
         <v>1</v>
       </c>
       <c r="E90">
-        <v>0.6333333333333333</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F90">
-        <v>0.7916666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -3670,10 +3670,10 @@
         <v>1</v>
       </c>
       <c r="E91">
-        <v>0.5333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F91">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G91">
         <v>0.5</v>
@@ -3699,13 +3699,13 @@
         <v>1</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E92">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F92">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -3760,16 +3760,16 @@
         <v>102</v>
       </c>
       <c r="C94">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D94">
         <v>0.5</v>
       </c>
       <c r="E94">
-        <v>0.5</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F94">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G94">
         <v>0.5</v>
@@ -3792,16 +3792,16 @@
         <v>103</v>
       </c>
       <c r="C95">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D95">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E95">
-        <v>0.4000000000000001</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F95">
-        <v>0.5</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -3824,16 +3824,16 @@
         <v>104</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>0.5666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F96">
-        <v>0.7083333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>0.4000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F97">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -3888,16 +3888,16 @@
         <v>106</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>0.5</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F98">
-        <v>0.625</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G98">
         <v>0.5</v>
@@ -3926,10 +3926,10 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F99">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -3958,10 +3958,10 @@
         <v>1</v>
       </c>
       <c r="E100">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F100">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -4131,19 +4131,19 @@
         <v>116</v>
       </c>
       <c r="B2">
-        <v>0.7072222222222223</v>
+        <v>0.7672460317460319</v>
       </c>
       <c r="C2">
         <v>0.6825</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>80</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4151,19 +4151,19 @@
         <v>117</v>
       </c>
       <c r="B3">
-        <v>0.715</v>
+        <v>0.7883333333333333</v>
       </c>
       <c r="C3">
         <v>0.68</v>
       </c>
       <c r="D3">
+        <v>24</v>
+      </c>
+      <c r="E3">
         <v>11</v>
       </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
       <c r="F3">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4171,19 +4171,19 @@
         <v>118</v>
       </c>
       <c r="B4">
-        <v>0.5337777777777777</v>
+        <v>0.5969259259259259</v>
       </c>
       <c r="C4">
         <v>0.5686666666666667</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4">
         <v>43</v>
-      </c>
-      <c r="F4">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4191,19 +4191,19 @@
         <v>119</v>
       </c>
       <c r="B5">
-        <v>0.6837367724867724</v>
+        <v>0.767063492063492</v>
       </c>
       <c r="C5">
         <v>0.7214682539682538</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="E5">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -4244,22 +4244,22 @@
         <v>116</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4267,22 +4267,22 @@
         <v>117</v>
       </c>
       <c r="B3">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>65</v>
+      </c>
+      <c r="D3">
         <v>11</v>
       </c>
-      <c r="C3">
-        <v>85</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
       <c r="E3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4290,22 +4290,22 @@
         <v>118</v>
       </c>
       <c r="B4">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4">
         <v>43</v>
       </c>
-      <c r="E4">
-        <v>43</v>
-      </c>
-      <c r="F4">
-        <v>44</v>
-      </c>
       <c r="G4">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4313,22 +4313,22 @@
         <v>119</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C5">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
